--- a/astro-site/public/dl/restaurant-financial-plan-templates/BONUS-08-what-if-scenario-simulator.xlsx
+++ b/astro-site/public/dl/restaurant-financial-plan-templates/BONUS-08-what-if-scenario-simulator.xlsx
@@ -155,7 +155,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -206,6 +206,9 @@
       <protection locked="0" hidden="0"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="4" fontId="8" fillId="4" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
       <protection locked="0" hidden="0"/>
@@ -724,7 +727,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:B19"/>
+  <dimension ref="A2:B20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -826,6 +829,13 @@
       <c r="B19" s="17" t="inlineStr">
         <is>
           <t>Version 2.0 · October 2026 · aichef.pro/en/digital-products/restaurant-financial-plan-templates · info@aichef.pro</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="30" customHeight="1">
+      <c r="B20" s="23" t="inlineStr">
+        <is>
+          <t>Planning tool, not financial, tax or legal advice. Requirements vary by state and city — check with your accountant and local authorities.</t>
         </is>
       </c>
     </row>
@@ -916,13 +926,13 @@
           <t>Average check (excl. sales tax)</t>
         </is>
       </c>
-      <c r="B6" s="23" t="n">
+      <c r="B6" s="24" t="n">
         <v>18</v>
       </c>
-      <c r="C6" s="23" t="n">
+      <c r="C6" s="24" t="n">
         <v>22</v>
       </c>
-      <c r="D6" s="23" t="n">
+      <c r="D6" s="24" t="n">
         <v>28</v>
       </c>
     </row>
@@ -991,18 +1001,18 @@
       </c>
     </row>
     <row r="11" ht="45" customHeight="1">
-      <c r="A11" s="24" t="inlineStr">
+      <c r="A11" s="25" t="inlineStr">
         <is>
           <t>Monthly fixed costs EXCLUDING labor and EXCLUDING the loan payment (rent, utilities, insurance, marketing, accounting / bookkeeping, other)</t>
         </is>
       </c>
-      <c r="B11" s="23" t="n">
+      <c r="B11" s="24" t="n">
         <v>6500</v>
       </c>
-      <c r="C11" s="23" t="n">
+      <c r="C11" s="24" t="n">
         <v>6200</v>
       </c>
-      <c r="D11" s="23" t="n">
+      <c r="D11" s="24" t="n">
         <v>5900</v>
       </c>
     </row>
@@ -1026,15 +1036,15 @@
           <t>Monthly revenue (excl. sales tax)</t>
         </is>
       </c>
-      <c r="B14" s="25">
+      <c r="B14" s="26">
         <f>B6*B7*B8</f>
         <v>18000.0</v>
       </c>
-      <c r="C14" s="25">
+      <c r="C14" s="26">
         <f>C6*C7*C8</f>
         <v>31460.0</v>
       </c>
-      <c r="D14" s="25">
+      <c r="D14" s="26">
         <f>D6*D7*D8</f>
         <v>56700.0</v>
       </c>
@@ -1045,15 +1055,15 @@
           <t>Food Cost</t>
         </is>
       </c>
-      <c r="B15" s="25">
+      <c r="B15" s="26">
         <f>B14*B9</f>
         <v>7200.0</v>
       </c>
-      <c r="C15" s="25">
+      <c r="C15" s="26">
         <f>C14*C9</f>
         <v>11011.0</v>
       </c>
-      <c r="D15" s="25">
+      <c r="D15" s="26">
         <f>D14*D9</f>
         <v>17010.0</v>
       </c>
@@ -1064,15 +1074,15 @@
           <t>Labor Cost</t>
         </is>
       </c>
-      <c r="B16" s="25">
+      <c r="B16" s="26">
         <f>B14*B10</f>
         <v>5760.0</v>
       </c>
-      <c r="C16" s="25">
+      <c r="C16" s="26">
         <f>C14*C10</f>
         <v>8808.800000000001</v>
       </c>
-      <c r="D16" s="25">
+      <c r="D16" s="26">
         <f>D14*D10</f>
         <v>14175.0</v>
       </c>
@@ -1083,15 +1093,15 @@
           <t>Fixed costs</t>
         </is>
       </c>
-      <c r="B17" s="25">
+      <c r="B17" s="26">
         <f>B11</f>
         <v>6500.0</v>
       </c>
-      <c r="C17" s="25">
+      <c r="C17" s="26">
         <f>C11</f>
         <v>6200.0</v>
       </c>
-      <c r="D17" s="25">
+      <c r="D17" s="26">
         <f>D11</f>
         <v>5900.0</v>
       </c>
@@ -1102,15 +1112,15 @@
           <t>TOTAL EXPENSES</t>
         </is>
       </c>
-      <c r="B18" s="25">
+      <c r="B18" s="26">
         <f>B15+B16+B17</f>
         <v>19460.0</v>
       </c>
-      <c r="C18" s="25">
+      <c r="C18" s="26">
         <f>C15+C16+C17</f>
         <v>26019.800000000003</v>
       </c>
-      <c r="D18" s="25">
+      <c r="D18" s="26">
         <f>D15+D16+D17</f>
         <v>37085.0</v>
       </c>
@@ -1121,15 +1131,15 @@
           <t>MONTHLY EBITDA</t>
         </is>
       </c>
-      <c r="B19" s="26">
+      <c r="B19" s="27">
         <f>B14-B18</f>
         <v>-1460.0</v>
       </c>
-      <c r="C19" s="26">
+      <c r="C19" s="27">
         <f>C14-C18</f>
         <v>5440.199999999997</v>
       </c>
-      <c r="D19" s="26">
+      <c r="D19" s="27">
         <f>D14-D18</f>
         <v>19615.0</v>
       </c>
@@ -1159,15 +1169,15 @@
           <t>ANNUAL EBITDA</t>
         </is>
       </c>
-      <c r="B21" s="26">
+      <c r="B21" s="27">
         <f>B19*12</f>
         <v>-17520.0</v>
       </c>
-      <c r="C21" s="26">
+      <c r="C21" s="27">
         <f>C19*12</f>
         <v>65282.399999999965</v>
       </c>
-      <c r="D21" s="26">
+      <c r="D21" s="27">
         <f>D19*12</f>
         <v>235380.0</v>
       </c>
@@ -1273,15 +1283,15 @@
           <t>Annual revenue (excl. sales tax)</t>
         </is>
       </c>
-      <c r="C4" s="25">
+      <c r="C4" s="26">
         <f>Simulator!B14*12</f>
         <v>216000.0</v>
       </c>
-      <c r="D4" s="25">
+      <c r="D4" s="26">
         <f>Simulator!C14*12</f>
         <v>377520.0</v>
       </c>
-      <c r="E4" s="25">
+      <c r="E4" s="26">
         <f>Simulator!D14*12</f>
         <v>680400.0</v>
       </c>
@@ -1292,15 +1302,15 @@
           <t>Annual Food Cost</t>
         </is>
       </c>
-      <c r="C5" s="25">
+      <c r="C5" s="26">
         <f>Simulator!B15*12</f>
         <v>86400.0</v>
       </c>
-      <c r="D5" s="25">
+      <c r="D5" s="26">
         <f>Simulator!C15*12</f>
         <v>132132.0</v>
       </c>
-      <c r="E5" s="25">
+      <c r="E5" s="26">
         <f>Simulator!D15*12</f>
         <v>204120.0</v>
       </c>
@@ -1311,15 +1321,15 @@
           <t>Annual Labor Cost</t>
         </is>
       </c>
-      <c r="C6" s="25">
+      <c r="C6" s="26">
         <f>Simulator!B16*12</f>
         <v>69120.0</v>
       </c>
-      <c r="D6" s="25">
+      <c r="D6" s="26">
         <f>Simulator!C16*12</f>
         <v>105705.6</v>
       </c>
-      <c r="E6" s="25">
+      <c r="E6" s="26">
         <f>Simulator!D16*12</f>
         <v>170100.0</v>
       </c>
@@ -1330,15 +1340,15 @@
           <t>Annual EBITDA</t>
         </is>
       </c>
-      <c r="C7" s="25">
+      <c r="C7" s="26">
         <f>Simulator!B21</f>
         <v>-17520.0</v>
       </c>
-      <c r="D7" s="25">
+      <c r="D7" s="26">
         <f>Simulator!C21</f>
         <v>65282.399999999965</v>
       </c>
-      <c r="E7" s="25">
+      <c r="E7" s="26">
         <f>Simulator!D21</f>
         <v>235380.0</v>
       </c>
